--- a/frontend/public/data/productos_inventario.xlsx
+++ b/frontend/public/data/productos_inventario.xlsx
@@ -2614,10 +2614,10 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>388</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -2659,10 +2659,10 @@
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>163</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -2704,10 +2704,10 @@
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -2749,10 +2749,10 @@
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>477</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -2794,10 +2794,10 @@
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>427</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -2837,16 +2837,12 @@
           <t>1 Unidad</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>344</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -2888,10 +2884,10 @@
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>85</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -2931,12 +2927,16 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -2978,10 +2978,10 @@
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>310</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -3023,10 +3023,10 @@
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>408</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -3066,12 +3066,16 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -3111,12 +3115,16 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>361</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -3158,10 +3166,10 @@
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>387</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -3203,10 +3211,10 @@
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>370</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -3246,16 +3254,12 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>240</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -3297,10 +3301,10 @@
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>256</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -3342,10 +3346,10 @@
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>366</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -3387,10 +3391,10 @@
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>493</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -3430,16 +3434,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>74</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>274</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
@@ -3530,10 +3530,10 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>292</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1">
@@ -3575,10 +3575,10 @@
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="n">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>102</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
@@ -3620,10 +3620,10 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>469</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
@@ -3665,10 +3665,10 @@
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
@@ -3710,10 +3710,10 @@
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>499</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" ht="60" customHeight="1">
@@ -3755,10 +3755,10 @@
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>351</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
@@ -3800,10 +3800,10 @@
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>253</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
@@ -3845,10 +3845,10 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>313</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" ht="60" customHeight="1">
@@ -3888,16 +3888,12 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>315</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
@@ -3937,16 +3933,12 @@
           <t>1 Paquete</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>161</v>
+        <v>367</v>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1">
@@ -3988,10 +3980,10 @@
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>60</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4031,12 +4023,16 @@
           <t>2 L</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>441</v>
+        <v>481</v>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1">
@@ -4076,16 +4072,12 @@
           <t>2 L</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>208</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1">
@@ -4127,10 +4119,10 @@
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>487</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1">
@@ -4172,10 +4164,10 @@
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>182</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37" ht="60" customHeight="1">
@@ -4221,10 +4213,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>354</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" ht="60" customHeight="1">
@@ -4266,10 +4258,10 @@
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>203</v>
+        <v>433</v>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1">
@@ -4309,12 +4301,16 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>52</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">
@@ -4354,16 +4350,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>338</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
@@ -4403,12 +4395,16 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="n">
         <v>98</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>168</v>
+        <v>471</v>
       </c>
     </row>
     <row r="42" ht="60" customHeight="1">
@@ -4448,16 +4444,12 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>349</v>
+        <v>495</v>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
@@ -4499,10 +4491,10 @@
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>355</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
@@ -4544,10 +4536,10 @@
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>294</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" ht="60" customHeight="1">
@@ -4587,16 +4579,12 @@
           <t>300g</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>82</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1">
@@ -4638,10 +4626,10 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>252</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" ht="60" customHeight="1">
@@ -4683,10 +4671,10 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>176</v>
+        <v>484</v>
       </c>
     </row>
     <row r="48" ht="60" customHeight="1">
@@ -4726,16 +4714,12 @@
           <t>50ml</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" ht="60" customHeight="1">
@@ -4777,10 +4761,10 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>143</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" ht="60" customHeight="1">
@@ -4822,10 +4806,10 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="n">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>204</v>
+        <v>472</v>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1">
@@ -4867,10 +4851,10 @@
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>138</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52" ht="60" customHeight="1">
@@ -4912,10 +4896,10 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>312</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" ht="60" customHeight="1">
@@ -4957,10 +4941,10 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>380</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" ht="60" customHeight="1">
@@ -5002,10 +4986,10 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" ht="60" customHeight="1">
@@ -5047,10 +5031,10 @@
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>411</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" ht="60" customHeight="1">
@@ -5092,10 +5076,10 @@
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>374</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57" ht="60" customHeight="1">
@@ -5135,16 +5119,12 @@
           <t>250ml</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>107</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" ht="60" customHeight="1">
@@ -5186,10 +5166,10 @@
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>422</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
@@ -5231,10 +5211,10 @@
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" ht="60" customHeight="1">
@@ -5274,16 +5254,12 @@
           <t>2 L</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>100</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" ht="60" customHeight="1">
@@ -5323,16 +5299,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>459</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" ht="60" customHeight="1">
@@ -5374,10 +5346,10 @@
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" ht="60" customHeight="1">
@@ -5419,10 +5391,10 @@
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="n">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>369</v>
+        <v>475</v>
       </c>
     </row>
     <row r="64" ht="60" customHeight="1">
@@ -5464,10 +5436,10 @@
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>364</v>
+        <v>252</v>
       </c>
     </row>
     <row r="65" ht="60" customHeight="1">
@@ -5509,10 +5481,10 @@
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>206</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" ht="60" customHeight="1">
@@ -5554,10 +5526,10 @@
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>321</v>
+        <v>487</v>
       </c>
     </row>
     <row r="67" ht="60" customHeight="1">
@@ -5599,10 +5571,10 @@
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>65</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" ht="60" customHeight="1">
@@ -5644,10 +5616,10 @@
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>276</v>
+        <v>253</v>
       </c>
     </row>
     <row r="69" ht="60" customHeight="1">
@@ -5687,12 +5659,16 @@
           <t>1 Unidad</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>323</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" ht="60" customHeight="1">
@@ -5734,10 +5710,10 @@
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" ht="60" customHeight="1">
@@ -5777,16 +5753,12 @@
           <t>10 Unidades</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>421</v>
+        <v>387</v>
       </c>
     </row>
     <row r="72" ht="60" customHeight="1">
@@ -5826,16 +5798,12 @@
           <t>Caja 36</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="n">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" ht="60" customHeight="1">
@@ -5877,10 +5845,10 @@
       </c>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>144</v>
+        <v>497</v>
       </c>
     </row>
     <row r="74" ht="60" customHeight="1">
@@ -5922,10 +5890,10 @@
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="n">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" ht="60" customHeight="1">
@@ -5967,10 +5935,10 @@
       </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="76" ht="60" customHeight="1">
@@ -6012,10 +5980,10 @@
       </c>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>241</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" ht="60" customHeight="1">
@@ -6055,16 +6023,12 @@
           <t>750ml</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>415</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" ht="60" customHeight="1">
@@ -6106,10 +6070,10 @@
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>160</v>
+        <v>281</v>
       </c>
     </row>
     <row r="79" ht="60" customHeight="1">
@@ -6151,10 +6115,10 @@
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>338</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" ht="60" customHeight="1">
@@ -6196,10 +6160,10 @@
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>54</v>
+        <v>476</v>
       </c>
     </row>
     <row r="81" ht="60" customHeight="1">
@@ -6239,16 +6203,12 @@
           <t>750ml</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>313</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" ht="60" customHeight="1">
@@ -6288,16 +6248,12 @@
           <t>750ml</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>260</v>
+        <v>470</v>
       </c>
     </row>
     <row r="83" ht="60" customHeight="1">
@@ -6339,14 +6295,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Oferta</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>81</v>
+        <v>479</v>
       </c>
     </row>
     <row r="84" ht="60" customHeight="1">
@@ -6388,10 +6344,10 @@
       </c>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="n">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>108</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/productos_inventario.xlsx
+++ b/frontend/public/data/productos_inventario.xlsx
@@ -2614,10 +2614,10 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>268</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -2659,10 +2659,10 @@
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>300</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -2702,12 +2702,16 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="n">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>332</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -2749,10 +2753,10 @@
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>147</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -2792,12 +2796,16 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>94</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -2837,12 +2845,16 @@
           <t>1 Unidad</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="n">
         <v>85</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>67</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -2884,10 +2896,10 @@
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>169</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -2927,16 +2939,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>330</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -2978,10 +2986,10 @@
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>104</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -3023,10 +3031,10 @@
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>481</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -3066,16 +3074,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>224</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -3115,16 +3119,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>240</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -3166,10 +3166,10 @@
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>262</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -3211,10 +3211,10 @@
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -3254,12 +3254,16 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>287</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -3301,10 +3305,10 @@
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>399</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -3346,10 +3350,10 @@
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -3391,10 +3395,10 @@
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -3436,10 +3440,10 @@
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>403</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -3479,16 +3483,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>338</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
@@ -3530,10 +3530,10 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>97</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1">
@@ -3573,12 +3573,16 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>163</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
@@ -3620,10 +3624,10 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>308</v>
+        <v>454</v>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
@@ -3665,10 +3669,10 @@
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>274</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
@@ -3710,10 +3714,10 @@
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="n">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>396</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" ht="60" customHeight="1">
@@ -3755,10 +3759,10 @@
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>220</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
@@ -3798,12 +3802,16 @@
           <t>250g</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>112</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
@@ -3845,10 +3853,10 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>488</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" ht="60" customHeight="1">
@@ -3890,10 +3898,10 @@
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="n">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>288</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
@@ -3935,10 +3943,10 @@
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>367</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1">
@@ -3978,12 +3986,16 @@
           <t>2 L</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>331</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4023,16 +4035,12 @@
           <t>2 L</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Oferta</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>481</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1">
@@ -4074,10 +4082,10 @@
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>356</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1">
@@ -4117,12 +4125,16 @@
           <t>2 L</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1">
@@ -4162,12 +4174,16 @@
           <t>1.5 L</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>235</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" ht="60" customHeight="1">
@@ -4207,16 +4223,12 @@
           <t>1 Kg</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>52</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" ht="60" customHeight="1">
@@ -4258,10 +4270,10 @@
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>433</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1">
@@ -4303,14 +4315,14 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Oferta</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="K39" s="2" t="n">
         <v>72</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>143</v>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">
@@ -4352,10 +4364,10 @@
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
@@ -4395,16 +4407,12 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>471</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" ht="60" customHeight="1">
@@ -4446,10 +4454,10 @@
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>495</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
@@ -4491,10 +4499,10 @@
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>192</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
@@ -4536,10 +4544,10 @@
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" ht="60" customHeight="1">
@@ -4581,10 +4589,10 @@
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>148</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1">
@@ -4626,10 +4634,10 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>341</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" ht="60" customHeight="1">
@@ -4669,12 +4677,16 @@
           <t>3 Unidades</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>484</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" ht="60" customHeight="1">
@@ -4714,12 +4726,16 @@
           <t>50ml</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>127</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" ht="60" customHeight="1">
@@ -4761,10 +4777,10 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" ht="60" customHeight="1">
@@ -4806,10 +4822,10 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>472</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1">
@@ -4851,10 +4867,10 @@
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>180</v>
+        <v>372</v>
       </c>
     </row>
     <row r="52" ht="60" customHeight="1">
@@ -4896,10 +4912,10 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>190</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" ht="60" customHeight="1">
@@ -4941,10 +4957,10 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>229</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" ht="60" customHeight="1">
@@ -4986,10 +5002,10 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="n">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>289</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" ht="60" customHeight="1">
@@ -5031,10 +5047,10 @@
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="n">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>337</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" ht="60" customHeight="1">
@@ -5074,12 +5090,16 @@
           <t>100 Unidades</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>280</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" ht="60" customHeight="1">
@@ -5121,10 +5141,10 @@
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>271</v>
+        <v>372</v>
       </c>
     </row>
     <row r="58" ht="60" customHeight="1">
@@ -5164,12 +5184,16 @@
           <t>100ml</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>157</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
@@ -5211,10 +5235,10 @@
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>74</v>
+        <v>341</v>
       </c>
     </row>
     <row r="60" ht="60" customHeight="1">
@@ -5256,10 +5280,10 @@
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>171</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" ht="60" customHeight="1">
@@ -5301,10 +5325,10 @@
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>173</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" ht="60" customHeight="1">
@@ -5344,12 +5368,16 @@
           <t>1 L</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>70</v>
+        <v>446</v>
       </c>
     </row>
     <row r="63" ht="60" customHeight="1">
@@ -5391,10 +5419,10 @@
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>475</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" ht="60" customHeight="1">
@@ -5436,10 +5464,10 @@
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>252</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65" ht="60" customHeight="1">
@@ -5481,10 +5509,10 @@
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>136</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" ht="60" customHeight="1">
@@ -5526,10 +5554,10 @@
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>487</v>
+        <v>435</v>
       </c>
     </row>
     <row r="67" ht="60" customHeight="1">
@@ -5569,12 +5597,16 @@
           <t>3 Unidades</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>161</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68" ht="60" customHeight="1">
@@ -5616,10 +5648,10 @@
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>253</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" ht="60" customHeight="1">
@@ -5659,16 +5691,12 @@
           <t>1 Unidad</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>113</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" ht="60" customHeight="1">
@@ -5710,10 +5738,10 @@
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>175</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" ht="60" customHeight="1">
@@ -5755,10 +5783,10 @@
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>387</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" ht="60" customHeight="1">
@@ -5800,10 +5828,10 @@
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>224</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" ht="60" customHeight="1">
@@ -5845,10 +5873,10 @@
       </c>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="74" ht="60" customHeight="1">
@@ -5888,12 +5916,16 @@
           <t>6 Pack</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>205</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" ht="60" customHeight="1">
@@ -5935,10 +5967,10 @@
       </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>325</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" ht="60" customHeight="1">
@@ -5980,10 +6012,10 @@
       </c>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>56</v>
+        <v>392</v>
       </c>
     </row>
     <row r="77" ht="60" customHeight="1">
@@ -6025,10 +6057,10 @@
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>261</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" ht="60" customHeight="1">
@@ -6070,10 +6102,10 @@
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>281</v>
+        <v>334</v>
       </c>
     </row>
     <row r="79" ht="60" customHeight="1">
@@ -6115,10 +6147,10 @@
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>226</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" ht="60" customHeight="1">
@@ -6160,10 +6192,10 @@
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>476</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" ht="60" customHeight="1">
@@ -6203,12 +6235,16 @@
           <t>750ml</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>132</v>
+        <v>274</v>
       </c>
     </row>
     <row r="82" ht="60" customHeight="1">
@@ -6250,10 +6286,10 @@
       </c>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K82" s="2" t="n">
         <v>52</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>470</v>
       </c>
     </row>
     <row r="83" ht="60" customHeight="1">
@@ -6295,14 +6331,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Oferta</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>479</v>
+        <v>498</v>
       </c>
     </row>
     <row r="84" ht="60" customHeight="1">
@@ -6342,12 +6378,16 @@
           <t>750ml</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>73</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/data/productos_inventario.xlsx
+++ b/frontend/public/data/productos_inventario.xlsx
@@ -156,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -181,6 +184,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -206,6 +212,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -231,6 +240,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -256,6 +268,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -281,6 +296,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -306,6 +324,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -331,6 +352,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -356,6 +380,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -381,6 +408,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -406,6 +436,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -431,6 +464,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -456,6 +492,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -481,6 +520,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -506,6 +548,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -531,6 +576,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -556,6 +604,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -581,6 +632,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -606,6 +660,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -631,6 +688,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -656,6 +716,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -681,6 +744,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -706,6 +772,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -731,6 +800,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -756,6 +828,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -781,6 +856,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -806,6 +884,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -831,6 +912,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -856,6 +940,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -881,6 +968,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -906,6 +996,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -931,6 +1024,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -956,6 +1052,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -981,6 +1080,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1006,6 +1108,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1031,6 +1136,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1056,6 +1164,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1081,6 +1192,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1106,6 +1220,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1131,6 +1248,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1156,6 +1276,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1181,6 +1304,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1206,6 +1332,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1231,6 +1360,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1256,6 +1388,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1281,6 +1416,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1306,6 +1444,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1331,6 +1472,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1356,6 +1500,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1381,6 +1528,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1406,6 +1556,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1431,6 +1584,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1456,6 +1612,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1481,6 +1640,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1506,6 +1668,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1531,6 +1696,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1556,6 +1724,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1581,6 +1752,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1606,6 +1780,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1631,6 +1808,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1656,6 +1836,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1681,6 +1864,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1706,6 +1892,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1731,6 +1920,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1756,6 +1948,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1781,6 +1976,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1806,6 +2004,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1831,6 +2032,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1856,6 +2060,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1881,6 +2088,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1906,6 +2116,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1931,6 +2144,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1956,6 +2172,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1981,6 +2200,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2006,6 +2228,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2031,6 +2256,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2056,6 +2284,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2081,6 +2312,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2106,6 +2340,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2131,6 +2368,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2156,6 +2396,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2181,6 +2424,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2206,6 +2452,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2583,13 +2832,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tomates Perita</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>$3.49</t>
-        </is>
+          <t>TOMATES PERITA X KG</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3.49</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -2632,13 +2879,11 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cebolla Blanca</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>$2.10</t>
-        </is>
+          <t>CEBOLLA INDIAN MOLIDA 55G</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3.29</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -2677,13 +2922,11 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Papa Lavada</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>$1.80</t>
-        </is>
+          <t>PAPAS X KG</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2.95</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -2726,13 +2969,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Zanahoria</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>$1.50</t>
-        </is>
+          <t>ZANAHORIAS X KG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2.89</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2771,13 +3012,11 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Pimenton Verde</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>$4.20</t>
-        </is>
+          <t>PIMENTON VERDE X KG</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3.75</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -2816,13 +3055,11 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Lechuga Romana</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>$1.20</t>
-        </is>
+          <t>LECHUGA ROMANA CULPROFRES 450G</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2.95</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -2861,13 +3098,11 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Platano Maduro</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>$1.90</t>
-        </is>
+          <t>PLATANO X KG</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2.79</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -2906,13 +3141,11 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cambur</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>$1.10</t>
-        </is>
+          <t>CAMBUR X KG</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1.35</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -2951,13 +3184,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Manzana Gala</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>$5.50</t>
-        </is>
+          <t>MANZANA ROYAL GALA X KG</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>5.25</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -2996,13 +3227,11 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Naranja para Jugo</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>$1.60</t>
-        </is>
+          <t>NARANJAS PARA JUGO X KG</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2.5</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -3045,13 +3274,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Lechosa</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>$1.75</t>
-        </is>
+          <t>LECHOSA X KG</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1.75</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -3094,13 +3321,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Limones</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>$4.19</t>
-        </is>
+          <t>LIMONES X KG</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4.19</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -3143,13 +3368,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Pina</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>$2.55</t>
-        </is>
+          <t>PIÑA X UN</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>2.55</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -3233,13 +3456,11 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Frutas Picadas Mixtas</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$3.00</t>
-        </is>
+          <t>PATILLA ROJA X KG</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1.19</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -3278,13 +3499,11 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Carne Molida SV</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>$9.95</t>
-        </is>
+          <t>CARNE MOLIDA SV</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>9.949999999999999</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -3372,13 +3591,11 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Costilla de Res</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>$7.80</t>
-        </is>
+          <t>COSTILLAS DE CERDO BBQ PREPARADOS PLAZAS CONGELADO X KG</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>21.95</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -3417,13 +3634,11 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Pechuga de Pollo</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>$8.45</t>
-        </is>
+          <t>PECHUGA DE POLLO MOLIDA X KG</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>11.45</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -3462,13 +3677,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Pollo Entero</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>$4.50</t>
-        </is>
+          <t>POLLO ENTERO UN POLLO PREMIUM X KG</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>4.45</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -3511,13 +3724,11 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Muslos de Pollo</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>$5.20</t>
-        </is>
+          <t>MUSLOS DE POLLO X KG</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>4.25</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -3556,13 +3767,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Alitas de Pollo</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>$6.00</t>
-        </is>
+          <t>DIADEX CREMA ANTIPAÑALITIS ALOE TUBO 50G</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>7.99</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -3601,13 +3810,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Jamon Cocido Plumrose</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>$6.50</t>
-        </is>
+          <t>JAMON ENDIABLADO PLUMROSE 60G</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>2.15</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -3646,13 +3853,11 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Queso Amarillo Paisa</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>$7.20</t>
-        </is>
+          <t>QUESO AMARILLO MAJU X KG</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>27.29</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -3691,13 +3896,11 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Queso Blanco Duro</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>$6.80</t>
-        </is>
+          <t>QUESO BLANCO MERIDEÑO X KG</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>10.99</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -3736,13 +3939,11 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Salchichas Plumrose</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>$4.50</t>
-        </is>
+          <t>SALCHICHAS FRANKFURT PLUMROSE DE 350G</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>9.890000000000001</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -3781,13 +3982,11 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tocino Ahumado</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>$4.80</t>
-        </is>
+          <t>TOCINETAS OINK PICANTE 110G</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1.69</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -3826,13 +4025,11 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Chorizo Carupanero</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>$5.50</t>
-        </is>
+          <t>CHORIZO MONTSERRATINA TIPO VELA X KG</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>52.88</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -3871,13 +4068,11 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Queso Guayanes</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>$4.50</t>
-        </is>
+          <t>QUESO GUAYANES X KG</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>8.19</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
@@ -3916,13 +4111,11 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Nuggets Congelados</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>$5.99</t>
-        </is>
+          <t>NUGGETS DE POLLO PLAZAS CONGELADOS X KG</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>13.44</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
@@ -3961,13 +4154,11 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Coca Cola Original</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>$2.50</t>
-        </is>
+          <t>COCA COLA SIN AZUCAR 2L</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1.44</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
@@ -4006,13 +4197,11 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Pepsi Cola</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>$2.20</t>
-        </is>
+          <t>PEPSI COLA 2L</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1.45</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
@@ -4051,13 +4240,11 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Chinotto</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>$2.20</t>
-        </is>
+          <t>CHINOTTO SIN CALORIAS 355CC</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0.79</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
@@ -4096,13 +4283,11 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Frescolita</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>$2.20</t>
-        </is>
+          <t>FRESCOLITA SIN CALORIAS 2L</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1.44</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
@@ -4141,13 +4326,11 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Maltin Polar</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>$2.00</t>
-        </is>
+          <t>MALTA MALTIN POLAR 1.5L</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1.93</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
@@ -4190,13 +4373,11 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Arroz Blanco Mary</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>$1.20</t>
-        </is>
+          <t>ARROZ MARY DORADO 800G</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1.75</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
@@ -4235,13 +4416,11 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Arroz Primor</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>$1.30</t>
-        </is>
+          <t>ARROZ PRIMOR TRADICIONAL 900G</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
@@ -4280,13 +4459,11 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Pasta Capri Espagueti</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>$1.60</t>
-        </is>
+          <t>PASTA CAPRI CANELONES 250G</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1.49</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -4325,13 +4502,11 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Harina PAN</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>$1.15</t>
-        </is>
+          <t>HARINA PAN MAIZ BLANCO GLUTEN FREE 2KG</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2.45</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
@@ -4374,13 +4549,11 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Caraotas Negras Mary</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>$1.80</t>
-        </is>
+          <t>CARAOTAS BLANCAS MARY 500G</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>3.4</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
@@ -4419,13 +4592,11 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Lentejas</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>$2.10</t>
-        </is>
+          <t>LENTEJAS MARY 400G</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1.8</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
@@ -4464,13 +4635,11 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Atun Margarita en Aceite</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>$2.50</t>
-        </is>
+          <t>ATUN MARGARITA EN ACEITE VEGETAL 140G</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>3.35</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
@@ -4509,13 +4678,11 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Atun Margarita en Agua</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>$2.50</t>
-        </is>
+          <t>ATUN MARGARITA AL NATURAL 140G</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
@@ -4554,13 +4721,11 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Maiz Dulce en Lata</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>$1.50</t>
-        </is>
+          <t>MAIZ DULCE CAUJARAL 4UN</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>7.9</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
@@ -4599,13 +4764,11 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Aceite de Maiz Mazeite</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>$3.50</t>
-        </is>
+          <t>ACEITE MAZEITE DE MAIZ 1L</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>5.8</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
@@ -4644,13 +4807,11 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Jabon Protex</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>$3.50</t>
-        </is>
+          <t>JABON LIQUIDO PROTEX DE AVENA 221ML</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>6.5</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
@@ -4689,13 +4850,11 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Desodorante Dove</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>$4.20</t>
-        </is>
+          <t>DESODORANTE ROLL ON DOVE DERMOACLARANTE 50ML</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>4.85</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
@@ -4734,13 +4893,11 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Crema Dental Colgate</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>$2.80</t>
-        </is>
+          <t>CEPILLO DENTAL COLGATE 360 MEDIO</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>4.74</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
@@ -4779,13 +4936,11 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Shampoo Pantene</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>$6.50</t>
-        </is>
+          <t>ACONDICIONADOR PANTENE RESTAURACION 400ML</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>11.34</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
@@ -4828,13 +4983,11 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Papel Higienico Scott</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>$3.80</t>
-        </is>
+          <t>PAPEL HIGIENICO SCOTT PREMIUM 4 ROLLOS</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>6.89</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
@@ -4873,13 +5026,11 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Toallas Sanitarias Always</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>$2.90</t>
-        </is>
+          <t>TOALLAS SANITARIAS ALWAYS ACTIVE NOCTURNAS 8UN</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>3.55</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
@@ -4918,13 +5069,11 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Maquina de Afeitar Gillette</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>$3.00</t>
-        </is>
+          <t>CARTUCHO GILLETTE VENUS SKIN COMFORT4UND</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>16.48</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
@@ -5008,13 +5157,11 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Algodon en Motas</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>$1.50</t>
-        </is>
+          <t>ALGODON ALGOBAP HIDROFILO 100G</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>5.68</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
@@ -5098,13 +5245,11 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Alcohol Isopropilico</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>$2.20</t>
-        </is>
+          <t>ALCOHOL DE QUEMAR OPIN 900ML</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>7.98</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
@@ -5143,13 +5288,11 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Agua Oxigenada</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>$1.00</t>
-        </is>
+          <t>AGUA OXIGENADA EL GUARDIAN 500ML</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2.85</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
@@ -5188,13 +5331,11 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Curitas Band-Aid</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>$3.00</t>
-        </is>
+          <t>CURITAS BRIUTCARE TRANSP X20 UN</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>4.29</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
@@ -5233,13 +5374,11 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Detergente Liquido Ariel</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>$8.50</t>
-        </is>
+          <t>DETERG LIQ ARIEL REVITACOLOR 1,8L</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
@@ -5278,13 +5417,11 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Detergente en Polvo ACE</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>$4.50</t>
-        </is>
+          <t>POLVO PARA HORNEAR OLYMPIA 120G</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>3.75</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
@@ -5327,13 +5464,11 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Suavizante Suavitel</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>$3.80</t>
-        </is>
+          <t>SUAVITEL COMPLETE FRESCA PRIMAVERA 1,3L</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>11.02</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
@@ -5372,13 +5507,11 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Lavaplatos Liquido Las Llaves</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>$2.50</t>
-        </is>
+          <t>DETERGENTE LAS LLAVES FLORAL POLVO 900G</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>4.34</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
@@ -5417,13 +5550,11 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Lavaplatos en Crema Axion</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>$1.80</t>
-        </is>
+          <t>LAVAPLATOS CREMA AXION BICAR 7 EN 1 450G</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>5.12</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
@@ -5462,13 +5593,11 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Cloro Nevex</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>$1.50</t>
-        </is>
+          <t>CLORO BONCLOR SUPER CLORO 4,5% 1L</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>2.15</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
@@ -5556,13 +5685,11 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Esponja Scotch-Brite</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>$3.50</t>
-        </is>
+          <t>ESPONJA ETERNA DOBLE USO 2UN</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>2.75</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -5650,13 +5777,11 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Escoba con Mango</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>$4.50</t>
-        </is>
+          <t>ESCOBA EL EGIPCIO PRECEIN</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>3.21</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
@@ -5695,13 +5820,11 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Coleto Tradicional</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>$2.00</t>
-        </is>
+          <t>COLETO ALGODON CLARA</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>4.34</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
@@ -5740,13 +5863,11 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Bolsas de Basura Grandes</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>$3.20</t>
-        </is>
+          <t>BOLSAS GRANCO PARA BASURA EXTRA RESISTENTES 60L X 6UN</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>2.42</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
@@ -5785,13 +5906,11 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Cerveza Polar Pilsen</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>$25.00</t>
-        </is>
+          <t>CERVEZA POLAR PILSEN LATA DE 250ML</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0.99</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
@@ -5830,13 +5949,11 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Cerveza Polar Light</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>$25.00</t>
-        </is>
+          <t>CERVEZA POLAR LIGHT LATA SLEEK DE 355ML</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1.06</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
@@ -5875,13 +5992,11 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Cerveza Solera Verde</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>$6.50</t>
-        </is>
+          <t>CERVEZA SOLERA LATA DE 250ML</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0.99</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
@@ -5920,13 +6035,11 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Cerveza Zulia</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>$6.00</t>
-        </is>
+          <t>CARBON EL ZULIA 3KG</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>12.6</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
@@ -5965,13 +6078,11 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Ron Santa Teresa Linaje</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>$18.00</t>
-        </is>
+          <t>VELON SANTA TERESA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>5.9</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
@@ -6010,13 +6121,11 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Ron Cacique Anejo</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>$12.00</t>
-        </is>
+          <t>RON CACIQUE 500 NUEVA IMAGEN 0,75L</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>15.51</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
@@ -6059,13 +6168,11 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Ron Pampero Aniversario</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>$22.00</t>
-        </is>
+          <t>SALSA DE TOMATE KETCHUP PAMPERO 397G</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>2.55</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
@@ -6108,13 +6215,11 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Ron Diplomatico Reserva Exclusiva</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>$35.00</t>
-        </is>
+          <t>RON CARUPANO RESERVA EXCLUSIVA 0,70L</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>19.01</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
@@ -6153,13 +6258,11 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Whisky Buchanan's 12 Anos</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>$42.00</t>
-        </is>
+          <t>WHISKY BUCHANANS DE LUXE 0,70 L</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>49.46</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
@@ -6198,13 +6301,11 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Whisky Old Parr 12 Anos</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>$38.00</t>
-        </is>
+          <t>WHISKY OLD PARR SILVER 0,75L</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>32.16</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
@@ -6247,13 +6348,11 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Vodka Gordon's</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>$10.00</t>
-        </is>
+          <t>VODKA GORDONS MANDARINA 0,70L</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>11.96</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
@@ -6296,13 +6395,11 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Vino Tinto Casillero del Diablo</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>$12.50</t>
-        </is>
+          <t>GUISANTES CON ZANAHORIAS DEL MONTE 411G</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>5.89</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>

--- a/frontend/public/data/productos_inventario.xlsx
+++ b/frontend/public/data/productos_inventario.xlsx
@@ -2879,11 +2879,11 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CEBOLLA INDIAN MOLIDA 55G</t>
+          <t>Cebolla Blanca X KG</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3.29</v>
+        <v>2.1</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -3055,11 +3055,11 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>LECHUGA ROMANA CULPROFRES 450G</t>
+          <t>Lechuga Romana</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2.95</v>
+        <v>1.2</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -3677,11 +3677,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>POLLO ENTERO UN POLLO PREMIUM X KG</t>
+          <t>Pollo Entero X KG</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -3767,11 +3767,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>DIADEX CREMA ANTIPAÑALITIS ALOE TUBO 50G</t>
+          <t>Alitas de Pollo X KG</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7.99</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -3982,11 +3982,11 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TOCINETAS OINK PICANTE 110G</t>
+          <t>Tocino Ahumado Plumrose 250G</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1.69</v>
+        <v>4.8</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Arroz</t>
+          <t>Harinas</t>
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Enlatados</t>
+          <t>Granos</t>
         </is>
       </c>
       <c r="F41" s="2" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Enlatados</t>
+          <t>Granos</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Arroz</t>
+          <t>Aceites</t>
         </is>
       </c>
       <c r="F46" s="2" t="n"/>
@@ -6035,11 +6035,11 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CARBON EL ZULIA 3KG</t>
+          <t>Cerveza Zulia 6 Pack</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>12.6</v>
+        <v>6</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
@@ -6078,11 +6078,11 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>VELON SANTA TERESA PRIMAVERA</t>
+          <t>Ron Santa Teresa Linaje 750ML</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
@@ -6168,11 +6168,11 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SALSA DE TOMATE KETCHUP PAMPERO 397G</t>
+          <t>Ron Pampero Aniversario 750ML</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2.55</v>
+        <v>22</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
@@ -6395,11 +6395,11 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>GUISANTES CON ZANAHORIAS DEL MONTE 411G</t>
+          <t>Vino Tinto Casillero del Diablo 750ML</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>5.89</v>
+        <v>12.5</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
@@ -6438,13 +6438,11 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Vino Blanco Santa Helena</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>$8.50</t>
-        </is>
+          <t>Vino Blanco Santa Helena 750ML</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>8.5</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
